--- a/test-cases/checkout-test-cases.xlsx
+++ b/test-cases/checkout-test-cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16980" activeTab="1"/>
+    <workbookView windowWidth="25800" windowHeight="17580"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="75">
   <si>
     <t>TC ID</t>
   </si>
@@ -137,13 +137,13 @@
 3. ข้อมูลในช่อง Last Name และ Zip/Postal Code ที่กรอกไว้ยังคงเดิม ไม่สูญหาย</t>
   </si>
   <si>
+    <t>Medium</t>
+  </si>
+  <si>
     <t>TC-CHECKOUT-003</t>
   </si>
   <si>
     <t>Verify Cancel from Checkout Information Page</t>
-  </si>
-  <si>
-    <t>Navigation</t>
   </si>
   <si>
     <t>1.ผู้ใช้เข้าสู่ระบบ (Login) สำเร็จด้วยบัญชี standard_user
@@ -205,9 +205,6 @@
   </si>
   <si>
     <t>Verify Order Summary and Price Calculation Accuracy</t>
-  </si>
-  <si>
-    <t>Calculation</t>
   </si>
   <si>
     <t xml:space="preserve">1.ผู้ใช้เข้าสู่ระบบ (Login) สำเร็จด้วยบัญชี standard_user
@@ -274,16 +271,10 @@
 4. บันทึกพฤติกรรมที่พบจริง และรอข้อกำหนดเรื่องรูปแบบ Postal Code ก่อนตัดสินว่าเป็น Defect</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>TC-CHECKOUT-007</t>
   </si>
   <si>
     <t>Verify Unauthenticated Checkout Access</t>
-  </si>
-  <si>
-    <t>Authorization</t>
   </si>
   <si>
     <t>1. Web Browser ถูกเปิดอยู่ และผู้ใช้ ยังไม่ได้เข้าสู่ระบบ (Not Logged In) หรือไม่มี Session / Active Cookie อยู่ในระบบ
@@ -1619,6 +1610,7 @@
     <col min="5" max="5" width="43.5" customWidth="1"/>
     <col min="6" max="6" width="58.25" customWidth="1"/>
     <col min="7" max="7" width="57.875" customWidth="1"/>
+    <col min="8" max="8" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:8">
@@ -1696,18 +1688,18 @@
         <v>22</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="118" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="4" t="s">
         <v>25</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -1722,7 +1714,7 @@
         <v>29</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="131" customHeight="1" spans="1:8">
@@ -1748,7 +1740,7 @@
         <v>35</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="151" customHeight="1" spans="1:8">
@@ -1758,20 +1750,20 @@
       <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>15</v>
@@ -1779,51 +1771,51 @@
     </row>
     <row r="7" ht="106" customHeight="1" spans="1:8">
       <c r="A7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="169" customHeight="1" spans="1:8">
       <c r="A8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>15</v>
@@ -2284,19 +2276,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" ht="224" customHeight="1" spans="1:6">
@@ -2304,13 +2296,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="5">
@@ -2322,13 +2314,13 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="5">
@@ -2337,16 +2329,16 @@
     </row>
     <row r="4" ht="92" customHeight="1" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="5">
@@ -2358,13 +2350,13 @@
         <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="5">
@@ -2376,13 +2368,13 @@
         <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="5">
@@ -2391,16 +2383,16 @@
     </row>
     <row r="7" ht="102" customHeight="1" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="5">
@@ -2409,16 +2401,16 @@
     </row>
     <row r="8" ht="130" customHeight="1" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="5">

--- a/test-cases/checkout-test-cases.xlsx
+++ b/test-cases/checkout-test-cases.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="199">
   <si>
     <t>SAUCEDEMO  /  CHECKOUT</t>
   </si>
@@ -217,13 +217,65 @@
     <t>Backpack ×1 at $29.99; Item Total $29.99; Tax $2.40; Total $32.39</t>
   </si>
   <si>
-    <t>Overview shows Backpack, quantity 1, $29.99; Item Total $29.99; Tax $2.40; Total $32.39. Payment Information displays "SauceCard #31337" and Shipping Information displays "Free Pony Express Delivery!".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Overview shows Backpack, quantity 1, $29.99; Item Total $29.99; Tax $2.40; Total $32.39. Payment Information displays "SauceCard #31337" and Shipping Information displays "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Free Pony Express Delivery!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
   <si>
     <t>Click Finish to place the order.</t>
   </si>
   <si>
-    <t>The browser navigates to /checkout-complete.html and displays "Thank you for your order!".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The browser navigates to /checkout-complete.html and displays "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Thank you for your order!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
   <si>
     <t>Check the cart badge after completing the order.</t>
@@ -256,7 +308,34 @@
     <t>10110</t>
   </si>
   <si>
-    <t>The user remains on /checkout-step-one.html. An error indicator and "Error: First Name is required" are displayed; navigation to Overview is blocked.</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The user remains on /checkout-step-one.html. An error indicator and "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Error: First Name is required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>" are displayed; navigation to Overview is blocked.</t>
+    </r>
   </si>
   <si>
     <t>Check that the entered Last Name and Postal Code remain after the validation error.</t>
@@ -403,7 +482,34 @@
     <t>Check the resulting page, redirection, and error message.</t>
   </si>
   <si>
-    <t>The browser redirects to https://www.saucedemo.com/; Checkout Information is inaccessible. Error: "Epic sadface: You can only access '/checkout-step-one.html' when you are logged in.".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The browser redirects to https://www.saucedemo.com/; Checkout Information is inaccessible. Error: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: You can only access '/checkout-step-one.html' when you are logged in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.".</t>
+    </r>
   </si>
   <si>
     <t>Leave the Zip/Postal Code field blank.</t>
@@ -412,7 +518,34 @@
     <t>Continue</t>
   </si>
   <si>
-    <t>The user remains on /checkout-step-one.html; the error "Error: Postal Code is required" is displayed, and navigation to Overview is blocked.</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The user remains on /checkout-step-one.html; the error "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Error: Postal Code is required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>" is displayed, and navigation to Overview is blocked.</t>
+    </r>
   </si>
   <si>
     <t>Verify that previously entered customer information is retained.</t>
@@ -427,6 +560,9 @@
     <t>MANUAL QA TEST DOCUMENTATION   •   TEST EXECUTION RESULTS</t>
   </si>
   <si>
+    <t>Evidence screenshots are grouped by Test Case ID, not individually mapped to each Actual Result entry. One screenshot may support multiple observations.</t>
+  </si>
+  <si>
     <t>Actual Result</t>
   </si>
   <si>
@@ -445,104 +581,396 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>1. Clicking Checkout opened /checkout-step-one.html.
-2. After the buyer information was entered, clicking Continue opened /checkout-step-two.html.
-3. Checkout Overview showed Backpack ×1 at $29.99.
-4. Item Total was $29.99; Tax was $2.40; Total was $32.39.
-5. Payment Information showed "SauceCard #31337"; Shipping Information showed "Free Pony Express Delivery!".
-6. Clicking Finish opened /checkout-complete.html and displayed "Thank you for your order!".
-7. The cart badge displayed no item count, and the cart was empty when revisited.</t>
+    <t>1. Clicking Checkout opened /checkout-step-one.html.</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_PRODUCTS.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_CART.png
-3. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_INFORMATION.png
-4. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_OVERVIEW.png
-5. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_COMPLETE.png
-6. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_EMPTY_CART.png</t>
-  </si>
-  <si>
-    <t>1. After clicking Continue, the user remained on Checkout: Your Information.
-2. A red "Error: First Name is required" message and error indicator appeared.
-3. Last Name "Doe" and Postal Code "10110" remained entered.</t>
-  </si>
-  <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-002_CART.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-002_BEFORE.png
-3. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-002_ERROR.png</t>
-  </si>
-  <si>
-    <t>1. Clicking Cancel returned the browser to /cart.html.
-2. Backpack and Bike Light remained in the cart, quantity 1 each.
-3. The cart badge still displayed 2.</t>
-  </si>
-  <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-003_BEFORE.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-003_INFORMATION.png
-3. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-003_AFTER.png</t>
-  </si>
-  <si>
-    <t>1. After clicking Continue, the user remained on Checkout: Your Information.
-2. A red "Error: Last Name is required" message and error indicator appeared.
-3. First Name "John" and Postal Code "10110" remained entered.</t>
-  </si>
-  <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-004_CART.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-004_BEFORE.png
-3. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-004_ERROR.png</t>
-  </si>
-  <si>
-    <t>1. Checkout Overview showed Backpack ×1 at $29.99 and Bike Light ×1 at $9.99.
-2. Item Total was $39.98; Tax was $3.20 (8%, rounded to two decimals); Total was $43.18.
-3. Payment Information displayed "SauceCard #31337".
-4. Shipping Information displayed "Free Pony Express Delivery!".</t>
-  </si>
-  <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_PRODUCTS.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_CART.png
-3. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_INFORMATION.png
-4. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_OVERVIEW.png</t>
-  </si>
-  <si>
-    <t>1. After clicking Continue, the application responded normally without freezing or crashing.
-2. The special-character Postal Code "@#$%" was accepted without a validation error.
-3. The application navigated to Checkout Overview and displayed product, payment, shipping, and pricing information.</t>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_PRODUCTS.png</t>
+  </si>
+  <si>
+    <t>2. After the buyer information was entered, clicking Continue opened /checkout-step-two.html.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_CART.png</t>
+  </si>
+  <si>
+    <t>3. Checkout Overview showed Backpack ×1 at $29.99.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_INFORMATION.png</t>
+  </si>
+  <si>
+    <t>4. Item Total was $29.99; Tax was $2.40; Total was $32.39.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_OVERVIEW.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5. Payment Information showed "SauceCard #31337"; Shipping Information showed "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Free Pony Express Delivery!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_COMPLETE.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6. Clicking Finish opened /checkout-complete.html and displayed "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Thank you for your order!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_EMPTY_CART.png</t>
+  </si>
+  <si>
+    <t>7. The cart badge displayed no item count, and the cart was empty when revisited.</t>
+  </si>
+  <si>
+    <t>1. After clicking Continue, the user remained on Checkout: Your Information.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-002_CART.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. A red "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Error: First Name is required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>" message and error indicator appeared.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-002_BEFORE.png</t>
+  </si>
+  <si>
+    <t>3. Last Name "Doe" and Postal Code "10110" remained entered.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-002_ERROR.png</t>
+  </si>
+  <si>
+    <t>1. Clicking Cancel returned the browser to /cart.html.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-003_BEFORE.png</t>
+  </si>
+  <si>
+    <t>2. Backpack and Bike Light remained in the cart, quantity 1 each.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-003_INFORMATION.png</t>
+  </si>
+  <si>
+    <t>3. The cart badge still displayed 2.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-003_AFTER.png</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-004_CART.png</t>
+  </si>
+  <si>
+    <t>2. A red "Error: Last Name is required" message and error indicator appeared.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-004_BEFORE.png</t>
+  </si>
+  <si>
+    <t>3. First Name "John" and Postal Code "10110" remained entered.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-004_ERROR.png</t>
+  </si>
+  <si>
+    <t>1. Checkout Overview showed Backpack ×1 at $29.99 and Bike Light ×1 at $9.99.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_PRODUCTS.png</t>
+  </si>
+  <si>
+    <t>2. Item Total was $39.98; Tax was $3.20 (8%, rounded to two decimals); Total was $43.18.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_CART.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. Payment Information displayed "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SauceCard #31337</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_INFORMATION.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4. Shipping Information displayed "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Free Pony Express Delivery!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_OVERVIEW.png</t>
+  </si>
+  <si>
+    <t>1. After clicking Continue, the application responded normally without freezing or crashing.</t>
   </si>
   <si>
     <t>NEEDS CLARIFICATION</t>
   </si>
   <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_CART.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_BEFORE.png
-3. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_OVERVIEW.png</t>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_CART.png</t>
   </si>
   <si>
     <t>NEEDS CLARIFICATION: Whether special characters should be accepted in Postal Code has no confirmed business acceptance criterion. This execution cannot be classified PASS/FAIL for input validation.
 The Postal Code field accepted @#$% and the application navigated to Overview. The project has no confirmed acceptance criterion defining permitted postal-code characters. The validation outcome therefore remains NEEDS CLARIFICATION; this is an assumption/requirements gap, not a confirmed defect.</t>
   </si>
   <si>
-    <t>1. Without logging in, opening /checkout-step-one.html did not display Checkout Information.
-2. The browser redirected to https://www.saucedemo.com/.
-3. The error appeared: "Epic sadface: You can only access '/checkout-step-one.html' when you are logged in."
-4. No checkout form or order data was accessible.</t>
-  </si>
-  <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-007_INCOGNITO.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-007_ACCESS_DENIED.png</t>
-  </si>
-  <si>
-    <t>1. The First Name field contained "John", and the Last Name field contained "Doe".
-2. The Zip/Postal Code field was left empty.
-3. After clicking Continue, the application displayed the error message "Error: Postal Code is required".
-4. The user remained on the Checkout: Your Information page.
-5. The previously entered First Name "John" and Last Name "Doe" were retained.</t>
-  </si>
-  <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-008_01_BEFORE.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-008_02_ERROR.png</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. The special-character Postal Code "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>@#$%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>" was accepted without a validation error.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_BEFORE.png</t>
+  </si>
+  <si>
+    <t>3. The application navigated to Checkout Overview and displayed product, payment, shipping, and pricing information.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_OVERVIEW.png</t>
+  </si>
+  <si>
+    <t>1. Without logging in, opening /checkout-step-one.html did not display Checkout Information.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-007_INCOGNITO.png</t>
+  </si>
+  <si>
+    <t>2. The browser redirected to https://www.saucedemo.com/.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. The error appeared: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Epic sadface: You can only access '/checkout-step-one.html' when you are logged in.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-007_ACCESS_DENIED.png</t>
+  </si>
+  <si>
+    <t>4. No checkout form or order data was accessible.</t>
+  </si>
+  <si>
+    <t>1. The First Name field contained "John", and the Last Name field contained "Doe".</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-008_01_BEFORE.png</t>
+  </si>
+  <si>
+    <t>2. The Zip/Postal Code field was left empty.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. After clicking Continue, the application displayed the error message "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Error: Postal Code is required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-008_02_ERROR.png</t>
+  </si>
+  <si>
+    <t>4. The user remained on the Checkout: Your Information page.</t>
+  </si>
+  <si>
+    <t>5. The previously entered First Name "John" and Last Name "Doe" were retained.</t>
   </si>
 </sst>
 </file>
@@ -556,7 +984,7 @@
     <numFmt numFmtId="179" formatCode="_-&quot;฿&quot;* #,##0_-;\-&quot;฿&quot;* #,##0_-;_-&quot;฿&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -584,6 +1012,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF002060"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color theme="3" tint="0.1"/>
@@ -604,6 +1038,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF98570A"/>
@@ -620,18 +1066,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -738,6 +1172,19 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -971,7 +1418,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1058,29 +1505,25 @@
     </border>
     <border>
       <left style="hair">
-        <color rgb="FF303944"/>
+        <color auto="1"/>
       </left>
       <right style="hair">
-        <color rgb="FF303944"/>
+        <color auto="1"/>
       </right>
-      <top style="hair">
-        <color rgb="FF303944"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF303944"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="hair">
-        <color rgb="FF303944"/>
+        <color auto="1"/>
       </left>
-      <right/>
-      <top style="hair">
-        <color rgb="FF303944"/>
-      </top>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="hair">
-        <color rgb="FF303944"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1112,6 +1555,21 @@
       <top/>
       <bottom style="hair">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FF303944"/>
+      </left>
+      <right style="hair">
+        <color rgb="FF303944"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF303944"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF303944"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1216,31 +1674,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1249,119 +1704,122 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1384,124 +1842,238 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1559,7 +2131,17 @@
   <dxfs count="22">
     <dxf>
       <font>
-        <color theme="9"/>
+        <color theme="5"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
@@ -1569,17 +2151,7 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0070C0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5"/>
+        <color theme="9"/>
       </font>
     </dxf>
     <dxf>
@@ -2016,24 +2588,24 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:7">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="66"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:7">
       <c r="A3" s="5" t="s">
@@ -2041,19 +2613,19 @@
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="68"/>
     </row>
     <row r="4" ht="11" customHeight="1" spans="1:7">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="35"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="71"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:7">
       <c r="A5" s="10" t="s">
@@ -2074,191 +2646,191 @@
       <c r="F5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="G5" s="80" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" ht="70" customHeight="1" spans="1:7">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="81" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="82" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="83" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1" spans="1:7">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="84" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="66" customHeight="1" spans="1:7">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="81" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="82" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="46" t="s">
+      <c r="F8" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="G8" s="83" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" ht="66" customHeight="1" spans="1:7">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="84" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" ht="66" customHeight="1" spans="1:7">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="81" t="s">
         <v>31</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="82" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="47" t="s">
+      <c r="G10" s="83" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" ht="66" customHeight="1" spans="1:7">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="84" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" ht="66" customHeight="1" spans="1:7">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="81" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="82" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="G12" s="83" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1" spans="1:7">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D13" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="49" t="s">
+      <c r="F13" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="84" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2293,40 +2865,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:5">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="29"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="32"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="66"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:5">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="6"/>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="34"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="68"/>
     </row>
     <row r="4" ht="11" customHeight="1" spans="1:5">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="35"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="71"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5">
       <c r="A5" s="10" t="s">
@@ -2346,633 +2918,633 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="73">
         <v>1</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="18" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" ht="29" customHeight="1" spans="1:5">
-      <c r="A7" s="39"/>
-      <c r="B7" s="37">
+      <c r="A7" s="74"/>
+      <c r="B7" s="73">
         <v>2</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
-      <c r="A8" s="39"/>
-      <c r="B8" s="37">
+      <c r="A8" s="74"/>
+      <c r="B8" s="73">
         <v>3</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="18" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" ht="72" customHeight="1" spans="1:5">
-      <c r="A9" s="39"/>
-      <c r="B9" s="37">
+      <c r="A9" s="74"/>
+      <c r="B9" s="73">
         <v>4</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="18" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5">
-      <c r="A10" s="39"/>
-      <c r="B10" s="37">
+      <c r="A10" s="74"/>
+      <c r="B10" s="73">
         <v>5</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="18" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="11" ht="29" customHeight="1" spans="1:5">
-      <c r="A11" s="39"/>
-      <c r="B11" s="37">
+      <c r="A11" s="74"/>
+      <c r="B11" s="73">
         <v>6</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12" ht="29" customHeight="1" spans="1:5">
-      <c r="A12" s="39"/>
-      <c r="B12" s="37">
+      <c r="A12" s="74"/>
+      <c r="B12" s="73">
         <v>7</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="18" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="13" ht="29" customHeight="1" spans="1:5">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="76">
         <v>1</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" ht="29" customHeight="1" spans="1:5">
-      <c r="A14" s="19"/>
-      <c r="B14" s="41">
+      <c r="A14" s="77"/>
+      <c r="B14" s="76">
         <v>2</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="15" ht="29" customHeight="1" spans="1:5">
-      <c r="A15" s="19"/>
-      <c r="B15" s="41">
+      <c r="A15" s="77"/>
+      <c r="B15" s="76">
         <v>3</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:5">
-      <c r="A16" s="19"/>
-      <c r="B16" s="41">
+      <c r="A16" s="77"/>
+      <c r="B16" s="76">
         <v>4</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="29" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
-      <c r="A17" s="19"/>
-      <c r="B17" s="41">
+      <c r="A17" s="77"/>
+      <c r="B17" s="76">
         <v>5</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="29" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="18" ht="29" customHeight="1" spans="1:5">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="73">
         <v>1</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="18" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" ht="29" customHeight="1" spans="1:5">
-      <c r="A19" s="39"/>
-      <c r="B19" s="37">
+      <c r="A19" s="74"/>
+      <c r="B19" s="73">
         <v>2</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="20" ht="29" customHeight="1" spans="1:5">
-      <c r="A20" s="39"/>
-      <c r="B20" s="37">
+      <c r="A20" s="74"/>
+      <c r="B20" s="73">
         <v>3</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="18" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="21" ht="29" customHeight="1" spans="1:5">
-      <c r="A21" s="39"/>
-      <c r="B21" s="37">
+      <c r="A21" s="74"/>
+      <c r="B21" s="73">
         <v>4</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E21" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="22" ht="29" customHeight="1" spans="1:5">
-      <c r="A22" s="39"/>
-      <c r="B22" s="37">
+      <c r="A22" s="74"/>
+      <c r="B22" s="73">
         <v>5</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="18" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="23" ht="29" customHeight="1" spans="1:5">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="41">
+      <c r="B23" s="76">
         <v>1</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" ht="29" customHeight="1" spans="1:5">
-      <c r="A24" s="19"/>
-      <c r="B24" s="41">
+      <c r="A24" s="77"/>
+      <c r="B24" s="76">
         <v>2</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" ht="29" customHeight="1" spans="1:5">
-      <c r="A25" s="19"/>
-      <c r="B25" s="41">
+      <c r="A25" s="77"/>
+      <c r="B25" s="76">
         <v>3</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="26" ht="55" customHeight="1" spans="1:5">
-      <c r="A26" s="19"/>
-      <c r="B26" s="41">
+      <c r="A26" s="77"/>
+      <c r="B26" s="76">
         <v>4</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="29" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="27" ht="29" customHeight="1" spans="1:5">
-      <c r="A27" s="19"/>
-      <c r="B27" s="41">
+      <c r="A27" s="77"/>
+      <c r="B27" s="76">
         <v>5</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="29" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:5">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="73">
         <v>1</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="38" t="s">
+      <c r="E28" s="18" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:5">
-      <c r="A29" s="39"/>
-      <c r="B29" s="37">
+      <c r="A29" s="74"/>
+      <c r="B29" s="73">
         <v>2</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="D29" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="38" t="s">
+      <c r="E29" s="18" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="30" ht="29" customHeight="1" spans="1:5">
-      <c r="A30" s="39"/>
-      <c r="B30" s="37">
+      <c r="A30" s="74"/>
+      <c r="B30" s="73">
         <v>3</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="38" t="s">
+      <c r="E30" s="18" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="31" ht="29" customHeight="1" spans="1:5">
-      <c r="A31" s="39"/>
-      <c r="B31" s="37">
+      <c r="A31" s="74"/>
+      <c r="B31" s="73">
         <v>4</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E31" s="38" t="s">
+      <c r="E31" s="18" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="32" ht="29" customHeight="1" spans="1:5">
-      <c r="A32" s="39"/>
-      <c r="B32" s="37">
+      <c r="A32" s="74"/>
+      <c r="B32" s="73">
         <v>5</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="D32" s="38" t="s">
+      <c r="D32" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="38" t="s">
+      <c r="E32" s="18" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="33" ht="29" customHeight="1" spans="1:5">
-      <c r="A33" s="40" t="s">
+      <c r="A33" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="41">
+      <c r="B33" s="76">
         <v>1</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="34" ht="29" customHeight="1" spans="1:5">
-      <c r="A34" s="19"/>
-      <c r="B34" s="41">
+      <c r="A34" s="77"/>
+      <c r="B34" s="76">
         <v>2</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="35" ht="29" customHeight="1" spans="1:5">
-      <c r="A35" s="19"/>
-      <c r="B35" s="41">
+      <c r="A35" s="77"/>
+      <c r="B35" s="76">
         <v>3</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1" spans="1:5">
-      <c r="A36" s="19"/>
-      <c r="B36" s="41">
+      <c r="A36" s="77"/>
+      <c r="B36" s="76">
         <v>4</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="29" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1" spans="1:5">
-      <c r="A37" s="19"/>
-      <c r="B37" s="41">
+      <c r="A37" s="77"/>
+      <c r="B37" s="76">
         <v>5</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="38" ht="29" customHeight="1" spans="1:5">
-      <c r="A38" s="19"/>
-      <c r="B38" s="41">
+      <c r="A38" s="77"/>
+      <c r="B38" s="76">
         <v>6</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="29" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1" spans="1:5">
-      <c r="A39" s="36" t="s">
+      <c r="A39" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="37">
+      <c r="B39" s="73">
         <v>1</v>
       </c>
-      <c r="C39" s="38" t="s">
+      <c r="C39" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D39" s="38" t="s">
+      <c r="D39" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E39" s="38" t="s">
+      <c r="E39" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1" spans="1:5">
-      <c r="A40" s="39"/>
-      <c r="B40" s="37">
+      <c r="A40" s="74"/>
+      <c r="B40" s="73">
         <v>2</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E40" s="38" t="s">
+      <c r="E40" s="18" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="41" ht="66" customHeight="1" spans="1:5">
-      <c r="A41" s="39"/>
-      <c r="B41" s="37">
+      <c r="A41" s="74"/>
+      <c r="B41" s="73">
         <v>3</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="38" t="s">
+      <c r="D41" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E41" s="38" t="s">
+      <c r="E41" s="18" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="42" ht="39" customHeight="1" spans="1:5">
-      <c r="A42" s="42" t="s">
+      <c r="A42" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="41">
+      <c r="B42" s="76">
         <v>1</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="43" ht="35" customHeight="1" spans="1:5">
-      <c r="A43" s="43"/>
-      <c r="B43" s="41">
+      <c r="A43" s="79"/>
+      <c r="B43" s="76">
         <v>2</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:5">
-      <c r="A44" s="43"/>
-      <c r="B44" s="41">
+      <c r="A44" s="79"/>
+      <c r="B44" s="76">
         <v>3</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1" spans="1:5">
-      <c r="A45" s="43"/>
-      <c r="B45" s="41">
+      <c r="A45" s="79"/>
+      <c r="B45" s="76">
         <v>4</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="29" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="46" ht="39" customHeight="1" spans="1:5">
-      <c r="A46" s="43"/>
-      <c r="B46" s="41">
+      <c r="A46" s="79"/>
+      <c r="B46" s="76">
         <v>5</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="29" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3002,13 +3574,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="65" customWidth="1"/>
+    <col min="2" max="2" width="89.75" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="69.375" customWidth="1"/>
+    <col min="4" max="4" width="94.75" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="65.75" customWidth="1"/>
@@ -3049,8 +3621,10 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" ht="11" customHeight="1" spans="1:7">
-      <c r="A4" s="8"/>
+    <row r="4" ht="23" customHeight="1" spans="1:7">
+      <c r="A4" s="8" t="s">
+        <v>132</v>
+      </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -3063,224 +3637,598 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" ht="237" customHeight="1" spans="1:7">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" ht="63" customHeight="1" spans="1:7">
       <c r="A6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D6" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15">
+      <c r="D6" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16">
         <v>46307</v>
       </c>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" ht="143" customHeight="1" spans="1:7">
-      <c r="A7" s="16" t="s">
+      <c r="G6" s="15"/>
+    </row>
+    <row r="7" ht="51" customHeight="1" spans="1:7">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="21"/>
+    </row>
+    <row r="8" ht="57" customHeight="1" spans="1:7">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="21"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="21"/>
+    </row>
+    <row r="9" ht="54" customHeight="1" spans="1:7">
+      <c r="A9" s="17"/>
+      <c r="B9" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="21"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="21"/>
+    </row>
+    <row r="10" ht="62" customHeight="1" spans="1:7">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" s="21"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="21"/>
+    </row>
+    <row r="11" ht="51" customHeight="1" spans="1:7">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="21"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="21"/>
+    </row>
+    <row r="12" ht="51" customHeight="1" spans="1:7">
+      <c r="A12" s="23"/>
+      <c r="B12" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="26"/>
+    </row>
+    <row r="13" ht="54" customHeight="1" spans="1:7">
+      <c r="A13" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20">
+      <c r="B13" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33">
         <v>46308</v>
       </c>
-      <c r="G7" s="19"/>
-    </row>
-    <row r="8" ht="135" customHeight="1" spans="1:7">
-      <c r="A8" s="11" t="s">
+      <c r="G13" s="32"/>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:7">
+      <c r="A14" s="34"/>
+      <c r="B14" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="35"/>
+      <c r="D14" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" s="36"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="36"/>
+    </row>
+    <row r="15" ht="54" customHeight="1" spans="1:7">
+      <c r="A15" s="38"/>
+      <c r="B15" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" ht="55" customHeight="1" spans="1:7">
+      <c r="A16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" s="14"/>
-      <c r="F8" s="15">
+      <c r="B16" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16">
         <v>46308</v>
       </c>
-      <c r="G8" s="14"/>
-    </row>
-    <row r="9" ht="141" customHeight="1" spans="1:7">
-      <c r="A9" s="16" t="s">
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" ht="59" customHeight="1" spans="1:7">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="21"/>
+    </row>
+    <row r="18" ht="54" customHeight="1" spans="1:7">
+      <c r="A18" s="23"/>
+      <c r="B18" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="26"/>
+    </row>
+    <row r="19" ht="59" customHeight="1" spans="1:7">
+      <c r="A19" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="20">
+      <c r="B19" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="33">
         <v>46308</v>
       </c>
-      <c r="G9" s="19"/>
-    </row>
-    <row r="10" ht="177" customHeight="1" spans="1:7">
-      <c r="A10" s="11" t="s">
+      <c r="G19" s="32"/>
+    </row>
+    <row r="20" ht="56" customHeight="1" spans="1:7">
+      <c r="A20" s="34"/>
+      <c r="B20" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="35"/>
+      <c r="D20" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="36"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="36"/>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:7">
+      <c r="A21" s="38"/>
+      <c r="B21" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="39"/>
+      <c r="D21" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="40"/>
+    </row>
+    <row r="22" ht="55" customHeight="1" spans="1:7">
+      <c r="A22" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="15">
+      <c r="B22" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16">
         <v>46308</v>
       </c>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" ht="120" customHeight="1" spans="1:7">
-      <c r="A11" s="16" t="s">
+      <c r="G22" s="15"/>
+    </row>
+    <row r="23" ht="58" customHeight="1" spans="1:7">
+      <c r="A23" s="17"/>
+      <c r="B23" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="E23" s="21"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="21"/>
+    </row>
+    <row r="24" ht="59" customHeight="1" spans="1:7">
+      <c r="A24" s="17"/>
+      <c r="B24" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="E24" s="21"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="21"/>
+    </row>
+    <row r="25" ht="54" customHeight="1" spans="1:7">
+      <c r="A25" s="23"/>
+      <c r="B25" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="24"/>
+      <c r="D25" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="26"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="26"/>
+    </row>
+    <row r="26" ht="60" customHeight="1" spans="1:7">
+      <c r="A26" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="20">
+      <c r="B26" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33">
         <v>46308</v>
       </c>
-      <c r="G11" s="17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="12" ht="120" customHeight="1" spans="1:7">
-      <c r="A12" s="11" t="s">
+      <c r="G26" s="44" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" ht="55" customHeight="1" spans="1:7">
+      <c r="A27" s="34"/>
+      <c r="B27" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="47"/>
+    </row>
+    <row r="28" ht="58" customHeight="1" spans="1:7">
+      <c r="A28" s="38"/>
+      <c r="B28" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="48"/>
+      <c r="D28" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="40"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="49"/>
+    </row>
+    <row r="29" ht="61" customHeight="1" spans="1:7">
+      <c r="A29" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="15">
+      <c r="B29" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="16">
         <v>46308</v>
       </c>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" ht="104" customHeight="1" spans="1:7">
-      <c r="A13" s="23" t="s">
+      <c r="G29" s="51"/>
+    </row>
+    <row r="30" ht="47" customHeight="1" spans="1:7">
+      <c r="A30" s="17"/>
+      <c r="B30" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="52"/>
+    </row>
+    <row r="31" ht="50" customHeight="1" spans="1:7">
+      <c r="A31" s="17"/>
+      <c r="B31" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="52"/>
+    </row>
+    <row r="32" ht="42" customHeight="1" spans="1:7">
+      <c r="A32" s="23"/>
+      <c r="B32" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="54"/>
+    </row>
+    <row r="33" ht="48" customHeight="1" spans="1:7">
+      <c r="A33" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="E13" s="24"/>
-      <c r="F13" s="20">
+      <c r="B33" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D33" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="E33" s="56"/>
+      <c r="F33" s="33">
         <v>46311</v>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G33" s="56"/>
+    </row>
+    <row r="34" ht="41" customHeight="1" spans="1:7">
+      <c r="A34" s="57"/>
+      <c r="B34" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34" s="35"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="58"/>
+    </row>
+    <row r="35" ht="42" customHeight="1" spans="1:7">
+      <c r="A35" s="57"/>
+      <c r="B35" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" s="35"/>
+      <c r="D35" s="59" t="s">
+        <v>196</v>
+      </c>
+      <c r="E35" s="58"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="58"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="1:7">
+      <c r="A36" s="57"/>
+      <c r="B36" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="C36" s="35"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="58"/>
+    </row>
+    <row r="37" ht="46" customHeight="1" spans="1:7">
+      <c r="A37" s="61"/>
+      <c r="B37" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="C37" s="39"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="50">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="C6:C12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="C33:C37"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="E6:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="E29:E32"/>
+    <mergeCell ref="E33:E37"/>
+    <mergeCell ref="F6:F12"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="F33:F37"/>
+    <mergeCell ref="G6:G12"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="G33:G37"/>
   </mergeCells>
-  <conditionalFormatting sqref="C13">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
-      <formula>"PASS"</formula>
+  <conditionalFormatting sqref="C33">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"NEEDS CLARIFICATION"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"FAIL"</formula>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"NOT RUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"BLOCKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"NOT RUN"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6 C13 C16 C19 C22 C26 C29">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"NEEDS CLARIFICATION"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:C12">
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
-      <formula>"FAIL"</formula>
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+      <formula>"NOT RUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"BLOCKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
-      <formula>"NOT RUN"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
+      <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
-      <formula>"NEEDS CLARIFICATION"</formula>
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+      <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C6:C13">
+    <dataValidation type="list" sqref="C6:C33">
       <formula1>"PASS,FAIL,BLOCKED,NOT RUN,NEEDS CLARIFICATION"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D6" r:id="rId1" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_PRODUCTS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_PRODUCTS.png"/>
+    <hyperlink ref="D13" r:id="rId2" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-002_CART.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-002_CART.png"/>
+    <hyperlink ref="D16" r:id="rId3" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-003_BEFORE.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-003_BEFORE.png"/>
+    <hyperlink ref="D19" r:id="rId4" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-004_CART.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-004_CART.png"/>
+    <hyperlink ref="D22" r:id="rId5" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_PRODUCTS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_PRODUCTS.png"/>
+    <hyperlink ref="D26" r:id="rId6" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_CART.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_CART.png"/>
+    <hyperlink ref="D29" r:id="rId7" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-007_INCOGNITO.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-007_INCOGNITO.png"/>
+    <hyperlink ref="D33" r:id="rId8" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-008_01_BEFORE.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-008_01_BEFORE.png"/>
+    <hyperlink ref="D9" r:id="rId9" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_OVERVIEW.png"/>
+    <hyperlink ref="D10" r:id="rId10" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_COMPLETE.png"/>
+    <hyperlink ref="D11" r:id="rId11" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_EMPTY_CART.png"/>
+    <hyperlink ref="D7" r:id="rId12" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_CART.png"/>
+    <hyperlink ref="D8" r:id="rId13" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-001_INFORMATION.png"/>
+    <hyperlink ref="D14" r:id="rId14" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-002_BEFORE.png"/>
+    <hyperlink ref="D15" r:id="rId15" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-002_ERROR.png"/>
+    <hyperlink ref="D17" r:id="rId16" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-003_INFORMATION.png"/>
+    <hyperlink ref="D18" r:id="rId17" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-003_AFTER.png"/>
+    <hyperlink ref="D20" r:id="rId18" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-004_BEFORE.png"/>
+    <hyperlink ref="D21" r:id="rId19" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-004_ERROR.png"/>
+    <hyperlink ref="D23" r:id="rId20" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_CART.png"/>
+    <hyperlink ref="D24" r:id="rId21" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_INFORMATION.png"/>
+    <hyperlink ref="D25" r:id="rId22" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-005_OVERVIEW.png"/>
+    <hyperlink ref="D27" r:id="rId23" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_BEFORE.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_BEFORE.png"/>
+    <hyperlink ref="D28" r:id="rId24" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-006_OVERVIEW.png"/>
+    <hyperlink ref="D31" r:id="rId25" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-007_ACCESS_DENIED.png"/>
+    <hyperlink ref="D35" r:id="rId26" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/checkout/TC-CHECKOUT-008_02_ERROR.png"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
